--- a/Projects/Datasets for Excel/Datasets for excel/data+for+statistics.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/data+for+statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/28. desc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B05AE38-393B-4D4A-97D0-14D0B45EB0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA515FC-8018-4F45-8782-8FB78249B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{03E43F0D-F947-F64B-9D7E-764189E7D68D}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{03E43F0D-F947-F64B-9D7E-764189E7D68D}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="64">
   <si>
     <t>Product_Category</t>
   </si>
@@ -227,6 +227,9 @@
   <si>
     <t>Count</t>
   </si>
+  <si>
+    <t>The descriptive analysis of 100 observations shows that the average discount rate is 18%, with a standard deviation of 7%. Its low positive skewness (0.17) indicates a relatively balanced distribution. Delivery time averages 4 days with a standard deviation of 2.04 days. Its positive skewness (0.72) indicates that longer delivery times occur more frequently than would be expected in a symmetric distribution, suggesting the presence of some relatively delayed deliveries.</t>
+  </si>
 </sst>
 </file>
 
@@ -337,12 +340,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -350,18 +351,32 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -377,9 +392,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -417,7 +432,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -523,7 +538,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -665,7 +680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -673,4470 +688,4687 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F7E85F-8E72-FD40-B371-05EEA98B0083}">
-  <dimension ref="A1:N101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S101"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="13">
         <v>619.41733832886609</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="12">
         <v>36.148044477110183</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="12">
         <v>4.5019279208872431</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="14">
         <v>0.28936177079024888</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="P2" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" s="15"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="13">
         <v>886.1339798802187</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="12">
         <v>22.67066139610537</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="12">
         <v>2.2397970835702168</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="14">
         <v>0.2207370029864176</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="13">
         <v>449.13093283360729</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="12">
         <v>25.659829377999021</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="12">
         <v>2.1554925808046521</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="14">
         <v>0.25439927348418562</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="P4" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>0.18142183732884562</v>
+      </c>
+      <c r="R4" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="18">
+        <v>4.439060939005028</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="13">
         <v>610.02358125508351</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="12">
         <v>22.71292327512996</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="12">
         <v>4.7441648170384667</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="14">
         <v>0.30629010595447159</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="P5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>7.2624387594151405E-3</v>
+      </c>
+      <c r="R5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="S5" s="17">
+        <v>0.20419658717095196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="13">
         <v>364.7761269469521</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="12">
         <v>22.17917729923893</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="14">
         <v>7.3005509594202878E-2</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="12">
         <v>2.750715816324262</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="14">
         <v>0.21021883294682961</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="P6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>0.18251118457953991</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S6" s="17">
+        <v>4.4498966056967122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="13">
         <v>576.61392133806294</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="12">
         <v>32.112950746165673</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="14">
         <v>0.17917733206862821</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="12">
         <v>4.5020717030418531</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="14">
         <v>0.29212239699142872</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="P7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>9.9897857119795777E-2</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="S7" s="17">
+        <v>2.6334829746684498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="13">
         <v>449.13093283360729</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="12">
         <v>34.168209673514582</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="14">
         <v>0.22561918398743461</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="12">
         <v>5.4069272717344461</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="14">
         <v>0.31072854455321491</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="P8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>7.2624387594151407E-2</v>
+      </c>
+      <c r="R8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="17">
+        <v>2.0419658717095195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="13">
         <v>372.90517238163818</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="12">
         <v>32.509503541037532</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="12">
         <v>2.1554925808046521</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="14">
         <v>0.2110494352398164</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="P9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>5.2743016734255318E-3</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="S9" s="17">
+        <v>4.1696246212264176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="13">
         <v>545.77266574920179</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="12">
         <v>28.966599379394442</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="12">
         <v>4.0998690570415128</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="14">
         <v>0.27918051659162052</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="P10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>-0.92997761939955836</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="S10" s="17">
+        <v>9.4281841148611267E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="13">
         <v>413.90524534251369</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="12">
         <v>22.800456610910508</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="12">
         <v>2.391060998990294</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="14">
         <v>0.22284298272060979</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="P11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>0.17117083920446693</v>
+      </c>
+      <c r="R11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="S11" s="17">
+        <v>0.71504386490503391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="13">
         <v>600.05114910613997</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="12">
         <v>37.920198615682011</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="14">
         <v>0.18251118457953991</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="12">
         <v>4.4498966056967122</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="14">
         <v>0.29895452589316301</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="P12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>0.281404108420785</v>
+      </c>
+      <c r="R12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="S12" s="17">
+        <v>10.157761616910481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="13">
         <v>726.81693567394757</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="12">
         <v>34.168209673514582</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="14">
         <v>0.25577787661114959</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="12">
         <v>7.2391498228691544</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="14">
         <v>0.35155019849350672</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="P13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>7.0450973374120401E-2</v>
+      </c>
+      <c r="R13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="S13" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="13">
         <v>491.90097738880718</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="12">
         <v>34.509555299643331</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="14">
         <v>0.17917733206862821</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="12">
         <v>2.2344005380713279</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14" s="14">
         <v>0.25465478640020989</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="P14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>0.35185508179490538</v>
+      </c>
+      <c r="R14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="S14" s="17">
+        <v>11.157761616910481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="13">
         <v>497.81317760107709</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="12">
         <v>34.233542912614041</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="14">
         <v>0.1810031805337412</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="12">
         <v>2.2397970835702168</v>
       </c>
-      <c r="N15" s="4">
+      <c r="N15" s="14">
         <v>0.2680229457328035</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="P15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>18.142183732884561</v>
+      </c>
+      <c r="R15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="S15" s="17">
+        <v>443.90609390050281</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="13">
         <v>734.54360210915809</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="12">
         <v>38.91018632957595</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="14">
         <v>0.27990155171090281</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="12">
         <v>7.7337485348890489</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="14">
         <v>0.35719492828615568</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="P16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>100</v>
+      </c>
+      <c r="R16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="S16" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="13">
         <v>610.02358125508351</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="12">
         <v>42.863547025446572</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="14">
         <v>0.30486450852597691</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="12">
         <v>8.5106816848864089</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N17" s="14">
         <v>0.40987566214717058</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="18" spans="1:19" ht="16.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="13">
         <v>614.24978057956264</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="12">
         <v>34.481965046749572</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="14">
         <v>0.22905363271008869</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="12">
         <v>5.4279598214684439</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N18" s="14">
         <v>0.31830109051492927</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="P18" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="13">
         <v>291.05760965024848</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="12">
         <v>19.701526021482589</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="14">
         <v>7.3005509594202878E-2</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="12">
         <v>2.391060998990294</v>
       </c>
-      <c r="N19" s="4">
+      <c r="N19" s="14">
         <v>0.17712869665622341</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="13">
         <v>696.81069761586082</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="12">
         <v>30.21220372182901</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="12">
         <v>4.4611863311108841</v>
       </c>
-      <c r="N20" s="4">
+      <c r="N20" s="14">
         <v>0.28515499329898969</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="13">
         <v>551.57500310812304</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="12">
         <v>42.328424856528947</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="14">
         <v>0.2498381806947613</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="12">
         <v>6.4350845115919242</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N21" s="14">
         <v>0.34135721988956752</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="13">
         <v>495.58882510192927</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="12">
         <v>25.761026144140789</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="14">
         <v>0.17917733206862821</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="12">
         <v>2.2344005380713279</v>
       </c>
-      <c r="N22" s="4">
+      <c r="N22" s="14">
         <v>0.25651376000433213</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="13">
         <v>252.880529766411</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="12">
         <v>32.124851019620138</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="14">
         <v>7.0450973374120401E-2</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="12">
         <v>1</v>
       </c>
-      <c r="N23" s="4">
+      <c r="N23" s="14">
         <v>0.14962905137318741</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="13">
         <v>294.05947140624812</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="12">
         <v>42.450393069510469</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="14">
         <v>7.3005509594202878E-2</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="12">
         <v>2.391060998990294</v>
       </c>
-      <c r="N24" s="4">
+      <c r="N24" s="14">
         <v>0.18294062777081871</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="13">
         <v>521.92242249612491</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K25" s="12">
         <v>27.640040591643441</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="14">
         <v>0.18479239883959939</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="12">
         <v>3.9722661653266131</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="14">
         <v>0.27367669906443659</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="13">
         <v>415.68001582094871</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="12">
         <v>23.1050477214369</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="12">
         <v>2.391060998990294</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="14">
         <v>0.22479924456866621</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="13">
         <v>463.17255028533771</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="12">
         <v>25.06958002405791</v>
       </c>
-      <c r="L27" s="4">
+      <c r="L27" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="12">
         <v>2.750715816324262</v>
       </c>
-      <c r="N27" s="4">
+      <c r="N27" s="14">
         <v>0.25128814980901171</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="13">
         <v>720.91010268149512</v>
       </c>
-      <c r="K28" s="3">
+      <c r="K28" s="12">
         <v>37.446775253972348</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="14">
         <v>0.25577787661114959</v>
       </c>
-      <c r="M28" s="3">
+      <c r="M28" s="12">
         <v>7.1168489736991756</v>
       </c>
-      <c r="N28" s="4">
+      <c r="N28" s="14">
         <v>0.34981255561364211</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="13">
         <v>830.13369852249514</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="12">
         <v>34.093862468973867</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="12">
         <v>4.0998690570415128</v>
       </c>
-      <c r="N29" s="4">
+      <c r="N29" s="14">
         <v>0.27568709704055427</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="13">
         <v>573.45234536559701</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="12">
         <v>31.988254494707039</v>
       </c>
-      <c r="L30" s="4">
+      <c r="L30" s="14">
         <v>0.17917733206862821</v>
       </c>
-      <c r="M30" s="3">
+      <c r="M30" s="12">
         <v>4.5020717030418531</v>
       </c>
-      <c r="N30" s="4">
+      <c r="N30" s="14">
         <v>0.2910865626887707</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="13">
         <v>473.55217273725202</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="12">
         <v>25.403001481665331</v>
       </c>
-      <c r="L31" s="4">
+      <c r="L31" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M31" s="3">
+      <c r="M31" s="12">
         <v>2.8369039927712101</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="14">
         <v>0.25301998160958439</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" s="11">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="13">
         <v>545.77266574920179</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="12">
         <v>42.957474570995288</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L32" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="12">
         <v>4.4498966056967122</v>
       </c>
-      <c r="N32" s="4">
+      <c r="N32" s="14">
         <v>0.28087418717400608</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="13">
         <v>375.22752388249648</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="12">
         <v>32.509503541037532</v>
       </c>
-      <c r="L33" s="4">
+      <c r="L33" s="14">
         <v>0.1810031805337412</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="12">
         <v>4.0998690570415128</v>
       </c>
-      <c r="N33" s="4">
+      <c r="N33" s="14">
         <v>0.29589157319362352</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="13">
         <v>610.02358125508351</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="12">
         <v>37.920198615682011</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34" s="14">
         <v>0.27131122626152698</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M34" s="12">
         <v>7.3585943681276529</v>
       </c>
-      <c r="N34" s="4">
+      <c r="N34" s="14">
         <v>0.3561087509382424</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="13">
         <v>830.13369852249514</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="12">
         <v>23.33189768406957</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="14">
         <v>0.28372444382937562</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="12">
         <v>6.763279513898901</v>
       </c>
-      <c r="N35" s="4">
+      <c r="N35" s="14">
         <v>0.37607345777717149</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="13">
         <v>307.91532286630729</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K36" s="12">
         <v>28.213310860324128</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M36" s="12">
         <v>2.6042442148223031</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="14">
         <v>0.18955232651186979</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="13">
         <v>557.79180936942089</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="12">
         <v>29.54505596450246</v>
       </c>
-      <c r="L37" s="4">
+      <c r="L37" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M37" s="12">
         <v>4.4498966056967122</v>
       </c>
-      <c r="N37" s="4">
+      <c r="N37" s="14">
         <v>0.28130963365436612</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="11">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="13">
         <v>449.13093283360729</v>
       </c>
-      <c r="K38" s="3">
+      <c r="K38" s="12">
         <v>42.450393069510469</v>
       </c>
-      <c r="L38" s="4">
+      <c r="L38" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M38" s="3">
+      <c r="M38" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N38" s="4">
+      <c r="N38" s="14">
         <v>0.24905707173957051</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="13">
         <v>734.54360210915809</v>
       </c>
-      <c r="K39" s="3">
+      <c r="K39" s="12">
         <v>36.148044477110183</v>
       </c>
-      <c r="L39" s="4">
+      <c r="L39" s="14">
         <v>0.27990155171090281</v>
       </c>
-      <c r="M39" s="3">
+      <c r="M39" s="12">
         <v>6.0080930310356884</v>
       </c>
-      <c r="N39" s="4">
+      <c r="N39" s="14">
         <v>0.35867859413871878</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="11">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="13">
         <v>252.880529766411</v>
       </c>
-      <c r="K40" s="3">
+      <c r="K40" s="12">
         <v>35.14527034142445</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40" s="14">
         <v>0.22905363271008869</v>
       </c>
-      <c r="M40" s="3">
+      <c r="M40" s="12">
         <v>5.622500309087072</v>
       </c>
-      <c r="N40" s="4">
+      <c r="N40" s="14">
         <v>0.32331029713287818</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="11">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="13">
         <v>708.1677590396705</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="12">
         <v>36.462644721053408</v>
       </c>
-      <c r="L41" s="4">
+      <c r="L41" s="14">
         <v>0.25577787661114959</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="12">
         <v>6.9431419019087111</v>
       </c>
-      <c r="N41" s="4">
+      <c r="N41" s="14">
         <v>0.34656380994048908</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="11">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="13">
         <v>447.27848635895299</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="12">
         <v>42.957474570995288</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="14">
         <v>0.30486450852597691</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="12">
         <v>8.929450265832779</v>
       </c>
-      <c r="N42" s="4">
+      <c r="N42" s="14">
         <v>0.41054204530787919</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="13">
         <v>890.46319359814106</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="12">
         <v>28.856357791851678</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="14">
         <v>0.35185508179490538</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="12">
         <v>11.157761616910481</v>
       </c>
-      <c r="N43" s="4">
+      <c r="N43" s="14">
         <v>0.45044823315321392</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="11">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="13">
         <v>503.2671201808941</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="12">
         <v>26.96311664321771</v>
       </c>
-      <c r="L44" s="4">
+      <c r="L44" s="14">
         <v>0.1810031805337412</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="12">
         <v>2.391060998990294</v>
       </c>
-      <c r="N44" s="4">
+      <c r="N44" s="14">
         <v>0.26813506639730089</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="11">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="13">
         <v>421.88563910474119</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="12">
         <v>24.258495432968651</v>
       </c>
-      <c r="L45" s="4">
+      <c r="L45" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="12">
         <v>2.6042442148223031</v>
       </c>
-      <c r="N45" s="4">
+      <c r="N45" s="14">
         <v>0.23379175927136131</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="11">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="13">
         <v>291.05760965024848</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="12">
         <v>30.21220372182901</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46" s="14">
         <v>0.27990155171090281</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="12">
         <v>6.0288776681174978</v>
       </c>
-      <c r="N46" s="4">
+      <c r="N46" s="14">
         <v>0.36212322494095361</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="11">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="13">
         <v>596.96015524763516</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="12">
         <v>32.640044751077639</v>
       </c>
-      <c r="L47" s="4">
+      <c r="L47" s="14">
         <v>0.18251118457953991</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="12">
         <v>4.0998690570415128</v>
       </c>
-      <c r="N47" s="4">
+      <c r="N47" s="14">
         <v>0.29718856991396142</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="11">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="13">
         <v>559.97758335747517</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="12">
         <v>30.116527726833709</v>
       </c>
-      <c r="L48" s="4">
+      <c r="L48" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="12">
         <v>4.4611863311108841</v>
       </c>
-      <c r="N48" s="4">
+      <c r="N48" s="14">
         <v>0.28336942798927012</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="11">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="13">
         <v>696.81069761586082</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="12">
         <v>36.329472046171738</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="14">
         <v>0.25577787661114959</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="12">
         <v>6.9102846410024767</v>
       </c>
-      <c r="N49" s="4">
+      <c r="N49" s="14">
         <v>0.34625154351267551</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="11">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="13">
         <v>606.72437794032601</v>
       </c>
-      <c r="K50" s="3">
+      <c r="K50" s="12">
         <v>33.488511070211693</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L50" s="14">
         <v>0.18479239883959939</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50" s="12">
         <v>4.4498966056967122</v>
       </c>
-      <c r="N50" s="4">
+      <c r="N50" s="14">
         <v>0.30257537012267921</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="13">
         <v>484.28885475832197</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K51" s="12">
         <v>22.67066139610537</v>
       </c>
-      <c r="L51" s="4">
+      <c r="L51" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M51" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N51" s="4">
+      <c r="N51" s="14">
         <v>0.25403672103000408</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="11">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="13">
         <v>504.65458741369969</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="12">
         <v>42.450393069510469</v>
       </c>
-      <c r="L52" s="4">
+      <c r="L52" s="14">
         <v>0.27990155171090281</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="12">
         <v>6.5150154200946098</v>
       </c>
-      <c r="N52" s="4">
+      <c r="N52" s="14">
         <v>0.3718495870650842</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="11">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="13">
         <v>496.06702576891882</v>
       </c>
-      <c r="K53" s="3">
+      <c r="K53" s="12">
         <v>26.6797836620513</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="14">
         <v>0.17917733206862821</v>
       </c>
-      <c r="M53" s="3">
+      <c r="M53" s="12">
         <v>2.2397970835702168</v>
       </c>
-      <c r="N53" s="4">
+      <c r="N53" s="14">
         <v>0.26525404584659262</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="11">
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="13">
         <v>569.036813905543</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="12">
         <v>37.510906147376723</v>
       </c>
-      <c r="L54" s="4">
+      <c r="L54" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="12">
         <v>4.5019279208872431</v>
       </c>
-      <c r="N54" s="4">
+      <c r="N54" s="14">
         <v>0.28728976709457338</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="11">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="13">
         <v>523.01127462814736</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K55" s="12">
         <v>21.014939592383691</v>
       </c>
-      <c r="L55" s="4">
+      <c r="L55" s="14">
         <v>0.27131122626152698</v>
       </c>
-      <c r="M55" s="3">
+      <c r="M55" s="12">
         <v>7.5553536437970177</v>
       </c>
-      <c r="N55" s="4">
+      <c r="N55" s="14">
         <v>0.35683679596408208</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="11">
         <v>55</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56" s="13">
         <v>438.67524693903368</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K56" s="12">
         <v>25.659829377999021</v>
       </c>
-      <c r="L56" s="4">
+      <c r="L56" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M56" s="3">
+      <c r="M56" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N56" s="4">
+      <c r="N56" s="14">
         <v>0.24060566113363149</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="11">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="13">
         <v>830.13369852249514</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="12">
         <v>42.819613509869228</v>
       </c>
-      <c r="L57" s="4">
+      <c r="L57" s="14">
         <v>0.28372444382937562</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="12">
         <v>8.3742832701451295</v>
       </c>
-      <c r="N57" s="4">
+      <c r="N57" s="14">
         <v>0.39777191437161191</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="11">
         <v>57</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="13">
         <v>497.81317760107709</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="12">
         <v>28.213310860324128</v>
       </c>
-      <c r="L58" s="4">
+      <c r="L58" s="14">
         <v>0.23905291654922339</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="12">
         <v>5.7331964921936969</v>
       </c>
-      <c r="N58" s="4">
+      <c r="N58" s="14">
         <v>0.33006229745372762</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
         <v>58</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="13">
         <v>375.22752388249648</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="12">
         <v>28.856357791851678</v>
       </c>
-      <c r="L59" s="4">
+      <c r="L59" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="12">
         <v>4.0998690570415128</v>
       </c>
-      <c r="N59" s="4">
+      <c r="N59" s="14">
         <v>0.27643788341618669</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="11">
         <v>59</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="13">
         <v>523.01127462814736</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="12">
         <v>32.509503541037532</v>
       </c>
-      <c r="L60" s="4">
+      <c r="L60" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="12">
         <v>3.9722661653266131</v>
       </c>
-      <c r="N60" s="4">
+      <c r="N60" s="14">
         <v>0.2743413460545816</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="11">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61" s="13">
         <v>504.65458741369969</v>
       </c>
-      <c r="K61" s="3">
+      <c r="K61" s="12">
         <v>36.13905882520546</v>
       </c>
-      <c r="L61" s="4">
+      <c r="L61" s="14">
         <v>0.2498381806947613</v>
       </c>
-      <c r="M61" s="3">
+      <c r="M61" s="12">
         <v>6.4232297561777791</v>
       </c>
-      <c r="N61" s="4">
+      <c r="N61" s="14">
         <v>0.34042130162395873</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="11">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="13">
         <v>319.56344705841639</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="12">
         <v>42.863547025446572</v>
       </c>
-      <c r="L62" s="4">
+      <c r="L62" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="12">
         <v>2.6042442148223031</v>
       </c>
-      <c r="N62" s="4">
+      <c r="N62" s="14">
         <v>0.19223505408993111</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="13">
         <v>619.41733832886609</v>
       </c>
-      <c r="K63" s="3">
+      <c r="K63" s="12">
         <v>34.543963455210843</v>
       </c>
-      <c r="L63" s="4">
+      <c r="L63" s="14">
         <v>0.22905363271008869</v>
       </c>
-      <c r="M63" s="3">
+      <c r="M63" s="12">
         <v>5.622500309087072</v>
       </c>
-      <c r="N63" s="4">
+      <c r="N63" s="14">
         <v>0.32266433225341751</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="11">
         <v>63</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="13">
         <v>305.47024795509333</v>
       </c>
-      <c r="K64" s="3">
+      <c r="K64" s="12">
         <v>20.833658043879868</v>
       </c>
-      <c r="L64" s="4">
+      <c r="L64" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M64" s="3">
+      <c r="M64" s="12">
         <v>2.6042442148223031</v>
       </c>
-      <c r="N64" s="4">
+      <c r="N64" s="14">
         <v>0.18679294537118299</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="13">
         <v>521.92242249612491</v>
       </c>
-      <c r="K65" s="3">
+      <c r="K65" s="12">
         <v>21.014939592383691</v>
       </c>
-      <c r="L65" s="4">
+      <c r="L65" s="14">
         <v>0.22561918398743461</v>
       </c>
-      <c r="M65" s="3">
+      <c r="M65" s="12">
         <v>4.7441648170384667</v>
       </c>
-      <c r="N65" s="4">
+      <c r="N65" s="14">
         <v>0.31044692368482418</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="11">
         <v>65</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="13">
         <v>473.37922936466907</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="12">
         <v>25.369547601790899</v>
       </c>
-      <c r="L66" s="4">
+      <c r="L66" s="14">
         <v>7.3005509594202878E-2</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="12">
         <v>2.750715816324262</v>
       </c>
-      <c r="N66" s="4">
+      <c r="N66" s="14">
         <v>0.25202637409654721</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="11">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="13">
         <v>619.41733832886609</v>
       </c>
-      <c r="K67" s="3">
+      <c r="K67" s="12">
         <v>37.510906147376723</v>
       </c>
-      <c r="L67" s="4">
+      <c r="L67" s="14">
         <v>0.27990155171090281</v>
       </c>
-      <c r="M67" s="3">
+      <c r="M67" s="12">
         <v>6.4350845115919242</v>
       </c>
-      <c r="N67" s="4">
+      <c r="N67" s="14">
         <v>0.37123395995440062</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="11">
         <v>67</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="13">
         <v>659.36358432663053</v>
       </c>
-      <c r="K68" s="3">
+      <c r="K68" s="12">
         <v>35.629086509343651</v>
       </c>
-      <c r="L68" s="4">
+      <c r="L68" s="14">
         <v>0.24660854919634351</v>
       </c>
-      <c r="M68" s="3">
+      <c r="M68" s="12">
         <v>5.7681308978786143</v>
       </c>
-      <c r="N68" s="4">
+      <c r="N68" s="14">
         <v>0.33292245175206381</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="11">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="13">
         <v>648.04278931605404</v>
       </c>
-      <c r="K69" s="3">
+      <c r="K69" s="12">
         <v>35.349709305309297</v>
       </c>
-      <c r="L69" s="4">
+      <c r="L69" s="14">
         <v>0.23270681750057659</v>
       </c>
-      <c r="M69" s="3">
+      <c r="M69" s="12">
         <v>5.6646280239591844</v>
       </c>
-      <c r="N69" s="4">
+      <c r="N69" s="14">
         <v>0.32581869835967092</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="11">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I70" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="13">
         <v>608.0353746788893</v>
       </c>
-      <c r="K70" s="3">
+      <c r="K70" s="12">
         <v>33.594994608612112</v>
       </c>
-      <c r="L70" s="4">
+      <c r="L70" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M70" s="3">
+      <c r="M70" s="12">
         <v>4.4611863311108841</v>
       </c>
-      <c r="N70" s="4">
+      <c r="N70" s="14">
         <v>0.30329966544333942</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="11">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I71" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="13">
         <v>362.0806959925111</v>
       </c>
-      <c r="K71" s="3">
+      <c r="K71" s="12">
         <v>21.830429874465541</v>
       </c>
-      <c r="L71" s="4">
+      <c r="L71" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M71" s="3">
+      <c r="M71" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N71" s="4">
+      <c r="N71" s="14">
         <v>0.20414723507989471</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="11">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I72" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72" s="13">
         <v>573.24211385453748</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="12">
         <v>31.780339128994552</v>
       </c>
-      <c r="L72" s="4">
+      <c r="L72" s="14">
         <v>0.17917733206862821</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="12">
         <v>4.5020717030418531</v>
       </c>
-      <c r="N72" s="4">
+      <c r="N72" s="14">
         <v>0.28948886558907888</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J73" s="13">
         <v>551.57500310812304</v>
       </c>
-      <c r="K73" s="3">
+      <c r="K73" s="12">
         <v>29.002436397815529</v>
       </c>
-      <c r="L73" s="4">
+      <c r="L73" s="14">
         <v>0.18491415701193711</v>
       </c>
-      <c r="M73" s="3">
+      <c r="M73" s="12">
         <v>4.4498966056967122</v>
       </c>
-      <c r="N73" s="4">
+      <c r="N73" s="14">
         <v>0.28054417581680913</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="11">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G74" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J74" s="13">
         <v>581.24124671152902</v>
       </c>
-      <c r="K74" s="3">
+      <c r="K74" s="12">
         <v>32.124851019620138</v>
       </c>
-      <c r="L74" s="4">
+      <c r="L74" s="14">
         <v>0.1810031805337412</v>
       </c>
-      <c r="M74" s="3">
+      <c r="M74" s="12">
         <v>4.5580608009335544</v>
       </c>
-      <c r="N74" s="4">
+      <c r="N74" s="14">
         <v>0.29284631491392171</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="11">
         <v>74</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I75" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J75" s="13">
         <v>551.57500310812304</v>
       </c>
-      <c r="K75" s="3">
+      <c r="K75" s="12">
         <v>39.870098609562831</v>
       </c>
-      <c r="L75" s="4">
+      <c r="L75" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M75" s="3">
+      <c r="M75" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N75" s="4">
+      <c r="N75" s="14">
         <v>0.20187766616909419</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A76">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="11">
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="I76" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="13">
         <v>545.77266574920179</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="12">
         <v>28.61134162948003</v>
       </c>
-      <c r="L76" s="4">
+      <c r="L76" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="12">
         <v>2.391060998990294</v>
       </c>
-      <c r="N76" s="4">
+      <c r="N76" s="14">
         <v>0.2248782794162171</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A77">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="11">
         <v>76</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I77" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="13">
         <v>403.40831801853841</v>
       </c>
-      <c r="K77" s="3">
+      <c r="K77" s="12">
         <v>22.71292327512996</v>
       </c>
-      <c r="L77" s="4">
+      <c r="L77" s="14">
         <v>7.3005509594202878E-2</v>
       </c>
-      <c r="M77" s="3">
+      <c r="M77" s="12">
         <v>2.2397970835702168</v>
       </c>
-      <c r="N77" s="4">
+      <c r="N77" s="14">
         <v>0.22107462398711211</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A78">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="11">
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="I78" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78" s="13">
         <v>886.1339798802187</v>
       </c>
-      <c r="K78" s="3">
+      <c r="K78" s="12">
         <v>21.380953935177011</v>
       </c>
-      <c r="L78" s="4">
+      <c r="L78" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M78" s="3">
+      <c r="M78" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N78" s="4">
+      <c r="N78" s="14">
         <v>0.19529177275776979</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A79">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="11">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="G79" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I79" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J79" s="13">
         <v>726.81693567394757</v>
       </c>
-      <c r="K79" s="3">
+      <c r="K79" s="12">
         <v>42.328424856528947</v>
       </c>
-      <c r="L79" s="4">
+      <c r="L79" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M79" s="3">
+      <c r="M79" s="12">
         <v>2.750715816324262</v>
       </c>
-      <c r="N79" s="4">
+      <c r="N79" s="14">
         <v>0.25414415926475448</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A80">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="11">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G80" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H80" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I80" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J80" s="13">
         <v>886.1339798802187</v>
       </c>
-      <c r="K80" s="3">
+      <c r="K80" s="12">
         <v>28.856357791851678</v>
       </c>
-      <c r="L80" s="4">
+      <c r="L80" s="14">
         <v>0.35185508179490538</v>
       </c>
-      <c r="M80" s="3">
+      <c r="M80" s="12">
         <v>9.1214958497639742</v>
       </c>
-      <c r="N80" s="4">
+      <c r="N80" s="14">
         <v>0.41063671974599147</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A81">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="11">
         <v>80</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="I81" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J81" s="1">
+      <c r="J81" s="13">
         <v>664.15565877204904</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="12">
         <v>35.712204079351267</v>
       </c>
-      <c r="L81" s="4">
+      <c r="L81" s="14">
         <v>0.24660854919634351</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="12">
         <v>6.0080930310356884</v>
       </c>
-      <c r="N81" s="4">
+      <c r="N81" s="14">
         <v>0.33781935185684459</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A82">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="11">
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G82" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="I82" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J82" s="13">
         <v>558.42480133446179</v>
       </c>
-      <c r="K82" s="3">
+      <c r="K82" s="12">
         <v>22.71292327512996</v>
       </c>
-      <c r="L82" s="4">
+      <c r="L82" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M82" s="3">
+      <c r="M82" s="12">
         <v>4.4611863311108841</v>
       </c>
-      <c r="N82" s="4">
+      <c r="N82" s="14">
         <v>0.28215109754040218</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A83">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="11">
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="I83" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83" s="13">
         <v>569.036813905543</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="12">
         <v>42.863547025446572</v>
       </c>
-      <c r="L83" s="4">
+      <c r="L83" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="12">
         <v>4.5019279208872431</v>
       </c>
-      <c r="N83" s="4">
+      <c r="N83" s="14">
         <v>0.28620642158906862</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A84">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="11">
         <v>83</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="G84" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H84" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="I84" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84" s="13">
         <v>252.880529766411</v>
       </c>
-      <c r="K84" s="3">
+      <c r="K84" s="12">
         <v>34.233542912614041</v>
       </c>
-      <c r="L84" s="4">
+      <c r="L84" s="14">
         <v>0.22905363271008869</v>
       </c>
-      <c r="M84" s="3">
+      <c r="M84" s="12">
         <v>5.4069272717344461</v>
       </c>
-      <c r="N84" s="4">
+      <c r="N84" s="14">
         <v>0.31094851703248888</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A85">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="11">
         <v>84</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="G85" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H85" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="I85" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="13">
         <v>773.23782906934002</v>
       </c>
-      <c r="K85" s="3">
+      <c r="K85" s="12">
         <v>41.422284810995777</v>
       </c>
-      <c r="L85" s="4">
+      <c r="L85" s="14">
         <v>0.27990155171090281</v>
       </c>
-      <c r="M85" s="3">
+      <c r="M85" s="12">
         <v>6.4232297561777791</v>
       </c>
-      <c r="N85" s="4">
+      <c r="N85" s="14">
         <v>0.36288404833129961</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="11">
         <v>85</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="G86" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="H86" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="I86" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86" s="13">
         <v>817.8805740858752</v>
       </c>
-      <c r="K86" s="3">
+      <c r="K86" s="12">
         <v>35.14527034142445</v>
       </c>
-      <c r="L86" s="4">
+      <c r="L86" s="14">
         <v>0.28372444382937562</v>
       </c>
-      <c r="M86" s="3">
+      <c r="M86" s="12">
         <v>8.2899354270025682</v>
       </c>
-      <c r="N86" s="4">
+      <c r="N86" s="14">
         <v>0.39096878987349809</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
         <v>86</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G87" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H87" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="I87" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87" s="13">
         <v>603.45495957616026</v>
       </c>
-      <c r="K87" s="3">
+      <c r="K87" s="12">
         <v>34.233542912614041</v>
       </c>
-      <c r="L87" s="4">
+      <c r="L87" s="14">
         <v>0.18424365288556879</v>
       </c>
-      <c r="M87" s="3">
+      <c r="M87" s="12">
         <v>4.4498966056967122</v>
       </c>
-      <c r="N87" s="4">
+      <c r="N87" s="14">
         <v>0.30025139260575129</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="11">
         <v>87</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="I88" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88" s="13">
         <v>518.08895796790466</v>
       </c>
-      <c r="K88" s="3">
+      <c r="K88" s="12">
         <v>34.509555299643331</v>
       </c>
-      <c r="L88" s="4">
+      <c r="L88" s="14">
         <v>0.22905363271008869</v>
       </c>
-      <c r="M88" s="3">
+      <c r="M88" s="12">
         <v>5.4279598214684439</v>
       </c>
-      <c r="N88" s="4">
+      <c r="N88" s="14">
         <v>0.31869611368775308</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="11">
         <v>88</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="G89" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="I89" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J89" s="13">
         <v>307.91532286630729</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="12">
         <v>34.093862468973867</v>
       </c>
-      <c r="L89" s="4">
+      <c r="L89" s="14">
         <v>0.25577787661114959</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="12">
         <v>6.763279513898901</v>
       </c>
-      <c r="N89" s="4">
+      <c r="N89" s="14">
         <v>0.34442553880212762</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A90">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="11">
         <v>89</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="G90" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="I90" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J90" s="13">
         <v>375.22752388249648</v>
       </c>
-      <c r="K90" s="3">
+      <c r="K90" s="12">
         <v>21.380953935177011</v>
       </c>
-      <c r="L90" s="4">
+      <c r="L90" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M90" s="3">
+      <c r="M90" s="12">
         <v>2.2344005380713279</v>
       </c>
-      <c r="N90" s="4">
+      <c r="N90" s="14">
         <v>0.21289820988431221</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A91">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="11">
         <v>90</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G91" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="I91" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J91" s="1">
+      <c r="J91" s="13">
         <v>519.22626043512992</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="12">
         <v>27.242540128268349</v>
       </c>
-      <c r="L91" s="4">
+      <c r="L91" s="14">
         <v>0.18424365288556879</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="12">
         <v>3.028547907328913</v>
       </c>
-      <c r="N91" s="4">
+      <c r="N91" s="14">
         <v>0.27060515784716049</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A92">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="11">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="G92" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="H92" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="I92" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="13">
         <v>291.05760965024848</v>
       </c>
-      <c r="K92" s="3">
+      <c r="K92" s="12">
         <v>39.870098609562831</v>
       </c>
-      <c r="L92" s="4">
+      <c r="L92" s="14">
         <v>0.24660854919634351</v>
       </c>
-      <c r="M92" s="3">
+      <c r="M92" s="12">
         <v>6.0288776681174978</v>
       </c>
-      <c r="N92" s="4">
+      <c r="N92" s="14">
         <v>0.33856809984859187</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A93">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="11">
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="G93" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="I93" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="13">
         <v>389.38710677341862</v>
       </c>
-      <c r="K93" s="3">
+      <c r="K93" s="12">
         <v>32.124851019620138</v>
       </c>
-      <c r="L93" s="4">
+      <c r="L93" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M93" s="3">
+      <c r="M93" s="12">
         <v>2.2344005380713279</v>
       </c>
-      <c r="N93" s="4">
+      <c r="N93" s="14">
         <v>0.21906150646039199</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A94">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="11">
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G94" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="I94" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94" s="13">
         <v>454.85168594785551</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="12">
         <v>21.380953935177011</v>
       </c>
-      <c r="L94" s="4">
+      <c r="L94" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="12">
         <v>2.750715816324262</v>
       </c>
-      <c r="N94" s="4">
+      <c r="N94" s="14">
         <v>0.24923385254589181</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A95">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="11">
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="G95" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="I95" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J95" s="1">
+      <c r="J95" s="13">
         <v>521.92242249612491</v>
       </c>
-      <c r="K95" s="3">
+      <c r="K95" s="12">
         <v>28.61134162948003</v>
       </c>
-      <c r="L95" s="4">
+      <c r="L95" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M95" s="3">
+      <c r="M95" s="12">
         <v>2.6042442148223031</v>
       </c>
-      <c r="N95" s="4">
+      <c r="N95" s="14">
         <v>0.23429928415438989</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A96">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" s="11">
         <v>95</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E96" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F96" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="G96" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H96" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="I96" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J96" s="13">
         <v>518.08895796790466</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="12">
         <v>37.920198615682011</v>
       </c>
-      <c r="L96" s="4">
+      <c r="L96" s="14">
         <v>0.18251118457953991</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="12">
         <v>3.028547907328913</v>
       </c>
-      <c r="N96" s="4">
+      <c r="N96" s="14">
         <v>0.26977427974324081</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A97">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="11">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="F97" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="G97" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="I97" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J97" s="1">
+      <c r="J97" s="13">
         <v>167.05152762488819</v>
       </c>
-      <c r="K97" s="3">
+      <c r="K97" s="12">
         <v>15.177312318503819</v>
       </c>
-      <c r="L97" s="4">
+      <c r="L97" s="14">
         <v>7.0450973374120401E-2</v>
       </c>
-      <c r="M97" s="3">
+      <c r="M97" s="12">
         <v>1</v>
       </c>
-      <c r="N97" s="4">
+      <c r="N97" s="14">
         <v>0.1227218508002173</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98" s="11">
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="G98" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="I98" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J98" s="1">
+      <c r="J98" s="13">
         <v>734.54360210915809</v>
       </c>
-      <c r="K98" s="3">
+      <c r="K98" s="12">
         <v>36.040297721835898</v>
       </c>
-      <c r="L98" s="4">
+      <c r="L98" s="14">
         <v>0.25577787661114959</v>
       </c>
-      <c r="M98" s="3">
+      <c r="M98" s="12">
         <v>6.5150154200946098</v>
       </c>
-      <c r="N98" s="4">
+      <c r="N98" s="14">
         <v>0.34288763100419523</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A99">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A99" s="11">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F99" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="I99" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J99" s="1">
+      <c r="J99" s="13">
         <v>447.27848635895299</v>
       </c>
-      <c r="K99" s="3">
+      <c r="K99" s="12">
         <v>24.86722617036456</v>
       </c>
-      <c r="L99" s="4">
+      <c r="L99" s="14">
         <v>0.16617445551725141</v>
       </c>
-      <c r="M99" s="3">
+      <c r="M99" s="12">
         <v>2.6334829746684498</v>
       </c>
-      <c r="N99" s="4">
+      <c r="N99" s="14">
         <v>0.24580046742972819</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A100">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100" s="11">
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="G100" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I100" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J100" s="1">
+      <c r="J100" s="13">
         <v>504.65458741369969</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="12">
         <v>25.659829377999021</v>
       </c>
-      <c r="L100" s="4">
+      <c r="L100" s="14">
         <v>0.18251118457953991</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="12">
         <v>2.9295153551612518</v>
       </c>
-      <c r="N100" s="4">
+      <c r="N100" s="14">
         <v>0.26928534750742977</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A101">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A101" s="11">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G101" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I101" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J101" s="13">
         <v>419.38042762271778</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="12">
         <v>36.13905882520546</v>
       </c>
-      <c r="L101" s="4">
+      <c r="L101" s="14">
         <v>9.9897857119795777E-2</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="12">
         <v>2.6042442148223031</v>
       </c>
-      <c r="N101" s="4">
+      <c r="N101" s="14">
         <v>0.23183287709095979</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P18:S27"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5144,36 +5376,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B9E6FC-7F28-1F4A-9631-C7F8F2D8822D}">
   <dimension ref="A1:G101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="str">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="str">
         <f>Data!J1</f>
         <v>Sales</v>
       </c>
-      <c r="B1" s="5" t="str">
+      <c r="B1" s="3" t="str">
         <f>Data!K1</f>
         <v>Quantity Sold</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="8"/>
+      <c r="F1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f>Data!J2</f>
         <v>619.41733832886609</v>
@@ -5182,12 +5414,12 @@
         <f>Data!K2</f>
         <v>36.148044477110183</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>Data!J3</f>
         <v>886.1339798802187</v>
@@ -5196,20 +5428,20 @@
         <f>Data!K3</f>
         <v>22.67066139610537</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="1">
         <v>535.26928258528517</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="1">
         <v>31.559208071450318</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f>Data!J4</f>
         <v>449.13093283360729</v>
@@ -5218,20 +5450,20 @@
         <f>Data!K4</f>
         <v>25.659829377999021</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="1">
         <v>15.823718386118008</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="1">
         <v>0.67879561329422011</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>Data!J5</f>
         <v>610.02358125508351</v>
@@ -5240,20 +5472,20 @@
         <f>Data!K5</f>
         <v>22.71292327512996</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="1">
         <v>522.46684856213619</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="1">
         <v>32.317177280328835</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>Data!J6</f>
         <v>364.7761269469521</v>
@@ -5262,20 +5494,20 @@
         <f>Data!K6</f>
         <v>22.17917729923893</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="1">
         <v>619.41733832886609</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="1">
         <v>25.659829377999021</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>Data!J7</f>
         <v>576.61392133806294</v>
@@ -5284,20 +5516,20 @@
         <f>Data!K7</f>
         <v>32.112950746165673</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="1">
         <v>158.23718386118009</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="1">
         <v>6.7879561329422016</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>Data!J8</f>
         <v>449.13093283360729</v>
@@ -5306,20 +5538,20 @@
         <f>Data!K8</f>
         <v>34.168209673514582</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="1">
         <v>25039.00635631691</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="1">
         <v>46.076348462747646</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>Data!J9</f>
         <v>372.90517238163818</v>
@@ -5328,20 +5560,20 @@
         <f>Data!K9</f>
         <v>32.509503541037532</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="1">
         <v>-0.11746249757267346</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="1">
         <v>-0.84273838049556371</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>Data!J10</f>
         <v>545.77266574920179</v>
@@ -5350,20 +5582,20 @@
         <f>Data!K10</f>
         <v>28.966599379394442</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="1">
         <v>0.23541228507435114</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="1">
         <v>-8.1175098339238139E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>Data!J11</f>
         <v>413.90524534251369</v>
@@ -5372,20 +5604,20 @@
         <f>Data!K11</f>
         <v>22.800456610910508</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="1">
         <v>723.41166597325287</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="1">
         <v>27.780162252491468</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>Data!J12</f>
         <v>600.05114910613997</v>
@@ -5394,20 +5626,20 @@
         <f>Data!K12</f>
         <v>37.920198615682011</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="1">
         <v>167.05152762488819</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="1">
         <v>15.177312318503819</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>Data!J13</f>
         <v>726.81693567394757</v>
@@ -5416,20 +5648,20 @@
         <f>Data!K13</f>
         <v>34.168209673514582</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="1">
         <v>890.46319359814106</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="1">
         <v>42.957474570995288</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>Data!J14</f>
         <v>491.90097738880718</v>
@@ -5438,20 +5670,20 @@
         <f>Data!K14</f>
         <v>34.509555299643331</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="1">
         <v>53526.928258528518</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="1">
         <v>3155.9208071450316</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f>Data!J15</f>
         <v>497.81317760107709</v>
@@ -5460,20 +5692,20 @@
         <f>Data!K15</f>
         <v>34.233542912614041</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="7">
         <v>100</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>Data!J16</f>
         <v>734.54360210915809</v>
@@ -5483,7 +5715,7 @@
         <v>38.91018632957595</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>Data!J17</f>
         <v>610.02358125508351</v>
@@ -5493,7 +5725,7 @@
         <v>42.863547025446572</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>Data!J18</f>
         <v>614.24978057956264</v>
@@ -5503,7 +5735,7 @@
         <v>34.481965046749572</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>Data!J19</f>
         <v>291.05760965024848</v>
@@ -5513,7 +5745,7 @@
         <v>19.701526021482589</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>Data!J20</f>
         <v>696.81069761586082</v>
@@ -5523,7 +5755,7 @@
         <v>30.21220372182901</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>Data!J21</f>
         <v>551.57500310812304</v>
@@ -5533,7 +5765,7 @@
         <v>42.328424856528947</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>Data!J22</f>
         <v>495.58882510192927</v>
@@ -5543,7 +5775,7 @@
         <v>25.761026144140789</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>Data!J23</f>
         <v>252.880529766411</v>
@@ -5553,7 +5785,7 @@
         <v>32.124851019620138</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>Data!J24</f>
         <v>294.05947140624812</v>
@@ -5563,7 +5795,7 @@
         <v>42.450393069510469</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>Data!J25</f>
         <v>521.92242249612491</v>
@@ -5573,7 +5805,7 @@
         <v>27.640040591643441</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>Data!J26</f>
         <v>415.68001582094871</v>
@@ -5583,7 +5815,7 @@
         <v>23.1050477214369</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>Data!J27</f>
         <v>463.17255028533771</v>
@@ -5593,7 +5825,7 @@
         <v>25.06958002405791</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>Data!J28</f>
         <v>720.91010268149512</v>
@@ -5603,7 +5835,7 @@
         <v>37.446775253972348</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>Data!J29</f>
         <v>830.13369852249514</v>
@@ -5613,7 +5845,7 @@
         <v>34.093862468973867</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>Data!J30</f>
         <v>573.45234536559701</v>
@@ -5623,7 +5855,7 @@
         <v>31.988254494707039</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>Data!J31</f>
         <v>473.55217273725202</v>
@@ -5633,7 +5865,7 @@
         <v>25.403001481665331</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>Data!J32</f>
         <v>545.77266574920179</v>
@@ -5643,7 +5875,7 @@
         <v>42.957474570995288</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>Data!J33</f>
         <v>375.22752388249648</v>
@@ -5653,7 +5885,7 @@
         <v>32.509503541037532</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>Data!J34</f>
         <v>610.02358125508351</v>
@@ -5663,7 +5895,7 @@
         <v>37.920198615682011</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>Data!J35</f>
         <v>830.13369852249514</v>
@@ -5673,7 +5905,7 @@
         <v>23.33189768406957</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>Data!J36</f>
         <v>307.91532286630729</v>
@@ -5683,7 +5915,7 @@
         <v>28.213310860324128</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>Data!J37</f>
         <v>557.79180936942089</v>
@@ -5693,7 +5925,7 @@
         <v>29.54505596450246</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f>Data!J38</f>
         <v>449.13093283360729</v>
@@ -5703,7 +5935,7 @@
         <v>42.450393069510469</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f>Data!J39</f>
         <v>734.54360210915809</v>
@@ -5713,7 +5945,7 @@
         <v>36.148044477110183</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f>Data!J40</f>
         <v>252.880529766411</v>
@@ -5723,7 +5955,7 @@
         <v>35.14527034142445</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f>Data!J41</f>
         <v>708.1677590396705</v>
@@ -5733,7 +5965,7 @@
         <v>36.462644721053408</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f>Data!J42</f>
         <v>447.27848635895299</v>
@@ -5743,7 +5975,7 @@
         <v>42.957474570995288</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f>Data!J43</f>
         <v>890.46319359814106</v>
@@ -5753,7 +5985,7 @@
         <v>28.856357791851678</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f>Data!J44</f>
         <v>503.2671201808941</v>
@@ -5763,7 +5995,7 @@
         <v>26.96311664321771</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <f>Data!J45</f>
         <v>421.88563910474119</v>
@@ -5773,7 +6005,7 @@
         <v>24.258495432968651</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <f>Data!J46</f>
         <v>291.05760965024848</v>
@@ -5783,7 +6015,7 @@
         <v>30.21220372182901</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <f>Data!J47</f>
         <v>596.96015524763516</v>
@@ -5793,7 +6025,7 @@
         <v>32.640044751077639</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <f>Data!J48</f>
         <v>559.97758335747517</v>
@@ -5803,7 +6035,7 @@
         <v>30.116527726833709</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <f>Data!J49</f>
         <v>696.81069761586082</v>
@@ -5813,7 +6045,7 @@
         <v>36.329472046171738</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <f>Data!J50</f>
         <v>606.72437794032601</v>
@@ -5823,7 +6055,7 @@
         <v>33.488511070211693</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <f>Data!J51</f>
         <v>484.28885475832197</v>
@@ -5833,7 +6065,7 @@
         <v>22.67066139610537</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <f>Data!J52</f>
         <v>504.65458741369969</v>
@@ -5843,7 +6075,7 @@
         <v>42.450393069510469</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <f>Data!J53</f>
         <v>496.06702576891882</v>
@@ -5853,7 +6085,7 @@
         <v>26.6797836620513</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <f>Data!J54</f>
         <v>569.036813905543</v>
@@ -5863,7 +6095,7 @@
         <v>37.510906147376723</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <f>Data!J55</f>
         <v>523.01127462814736</v>
@@ -5873,7 +6105,7 @@
         <v>21.014939592383691</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <f>Data!J56</f>
         <v>438.67524693903368</v>
@@ -5883,7 +6115,7 @@
         <v>25.659829377999021</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <f>Data!J57</f>
         <v>830.13369852249514</v>
@@ -5893,7 +6125,7 @@
         <v>42.819613509869228</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <f>Data!J58</f>
         <v>497.81317760107709</v>
@@ -5903,7 +6135,7 @@
         <v>28.213310860324128</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <f>Data!J59</f>
         <v>375.22752388249648</v>
@@ -5913,7 +6145,7 @@
         <v>28.856357791851678</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <f>Data!J60</f>
         <v>523.01127462814736</v>
@@ -5923,7 +6155,7 @@
         <v>32.509503541037532</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <f>Data!J61</f>
         <v>504.65458741369969</v>
@@ -5933,7 +6165,7 @@
         <v>36.13905882520546</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <f>Data!J62</f>
         <v>319.56344705841639</v>
@@ -5943,7 +6175,7 @@
         <v>42.863547025446572</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <f>Data!J63</f>
         <v>619.41733832886609</v>
@@ -5953,7 +6185,7 @@
         <v>34.543963455210843</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <f>Data!J64</f>
         <v>305.47024795509333</v>
@@ -5963,7 +6195,7 @@
         <v>20.833658043879868</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <f>Data!J65</f>
         <v>521.92242249612491</v>
@@ -5973,7 +6205,7 @@
         <v>21.014939592383691</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <f>Data!J66</f>
         <v>473.37922936466907</v>
@@ -5983,7 +6215,7 @@
         <v>25.369547601790899</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <f>Data!J67</f>
         <v>619.41733832886609</v>
@@ -5993,7 +6225,7 @@
         <v>37.510906147376723</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <f>Data!J68</f>
         <v>659.36358432663053</v>
@@ -6003,7 +6235,7 @@
         <v>35.629086509343651</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <f>Data!J69</f>
         <v>648.04278931605404</v>
@@ -6013,7 +6245,7 @@
         <v>35.349709305309297</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <f>Data!J70</f>
         <v>608.0353746788893</v>
@@ -6023,7 +6255,7 @@
         <v>33.594994608612112</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <f>Data!J71</f>
         <v>362.0806959925111</v>
@@ -6033,7 +6265,7 @@
         <v>21.830429874465541</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <f>Data!J72</f>
         <v>573.24211385453748</v>
@@ -6043,7 +6275,7 @@
         <v>31.780339128994552</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <f>Data!J73</f>
         <v>551.57500310812304</v>
@@ -6053,7 +6285,7 @@
         <v>29.002436397815529</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <f>Data!J74</f>
         <v>581.24124671152902</v>
@@ -6063,7 +6295,7 @@
         <v>32.124851019620138</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <f>Data!J75</f>
         <v>551.57500310812304</v>
@@ -6073,7 +6305,7 @@
         <v>39.870098609562831</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <f>Data!J76</f>
         <v>545.77266574920179</v>
@@ -6083,7 +6315,7 @@
         <v>28.61134162948003</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <f>Data!J77</f>
         <v>403.40831801853841</v>
@@ -6093,7 +6325,7 @@
         <v>22.71292327512996</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <f>Data!J78</f>
         <v>886.1339798802187</v>
@@ -6103,7 +6335,7 @@
         <v>21.380953935177011</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <f>Data!J79</f>
         <v>726.81693567394757</v>
@@ -6113,7 +6345,7 @@
         <v>42.328424856528947</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <f>Data!J80</f>
         <v>886.1339798802187</v>
@@ -6123,7 +6355,7 @@
         <v>28.856357791851678</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <f>Data!J81</f>
         <v>664.15565877204904</v>
@@ -6133,7 +6365,7 @@
         <v>35.712204079351267</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <f>Data!J82</f>
         <v>558.42480133446179</v>
@@ -6143,7 +6375,7 @@
         <v>22.71292327512996</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <f>Data!J83</f>
         <v>569.036813905543</v>
@@ -6153,7 +6385,7 @@
         <v>42.863547025446572</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <f>Data!J84</f>
         <v>252.880529766411</v>
@@ -6163,7 +6395,7 @@
         <v>34.233542912614041</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <f>Data!J85</f>
         <v>773.23782906934002</v>
@@ -6173,7 +6405,7 @@
         <v>41.422284810995777</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <f>Data!J86</f>
         <v>817.8805740858752</v>
@@ -6183,7 +6415,7 @@
         <v>35.14527034142445</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <f>Data!J87</f>
         <v>603.45495957616026</v>
@@ -6193,7 +6425,7 @@
         <v>34.233542912614041</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <f>Data!J88</f>
         <v>518.08895796790466</v>
@@ -6203,7 +6435,7 @@
         <v>34.509555299643331</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <f>Data!J89</f>
         <v>307.91532286630729</v>
@@ -6213,7 +6445,7 @@
         <v>34.093862468973867</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <f>Data!J90</f>
         <v>375.22752388249648</v>
@@ -6223,7 +6455,7 @@
         <v>21.380953935177011</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <f>Data!J91</f>
         <v>519.22626043512992</v>
@@ -6233,7 +6465,7 @@
         <v>27.242540128268349</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <f>Data!J92</f>
         <v>291.05760965024848</v>
@@ -6243,7 +6475,7 @@
         <v>39.870098609562831</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <f>Data!J93</f>
         <v>389.38710677341862</v>
@@ -6253,7 +6485,7 @@
         <v>32.124851019620138</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <f>Data!J94</f>
         <v>454.85168594785551</v>
@@ -6263,7 +6495,7 @@
         <v>21.380953935177011</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <f>Data!J95</f>
         <v>521.92242249612491</v>
@@ -6273,7 +6505,7 @@
         <v>28.61134162948003</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <f>Data!J96</f>
         <v>518.08895796790466</v>
@@ -6283,7 +6515,7 @@
         <v>37.920198615682011</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <f>Data!J97</f>
         <v>167.05152762488819</v>
@@ -6293,7 +6525,7 @@
         <v>15.177312318503819</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <f>Data!J98</f>
         <v>734.54360210915809</v>
@@ -6303,7 +6535,7 @@
         <v>36.040297721835898</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <f>Data!J99</f>
         <v>447.27848635895299</v>
@@ -6313,7 +6545,7 @@
         <v>24.86722617036456</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <f>Data!J100</f>
         <v>504.65458741369969</v>
@@ -6323,7 +6555,7 @@
         <v>25.659829377999021</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <f>Data!J101</f>
         <v>419.38042762271778</v>
